--- a/测试用例清单.xlsx
+++ b/测试用例清单.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sml\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B943FE35-D8AA-4135-A015-DEFCD74E7AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26807FE-7211-42BE-A1EE-5D0A28A6E904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="108">
   <si>
     <t>在此处概述本测试用例</t>
   </si>
@@ -1661,6 +1661,129 @@
     <t>不报错，正常返回类数据</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>check_content</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入内容测试：正常输入</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我想学习</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>基础语法</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>将输入测试文本传入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>check_content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>函数，判断返回值与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>expected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否一致</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入内容测试：包含敏感词</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>请帮我出一套关于赌博危害的题目</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入内容测试：空字符串</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>""</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入测试内容：近似敏感词</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>这段代码性能爆破式提升，效率翻倍</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>将输入测试文本传入check_content函数，判断返回值与expected是否一致</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2158,6 +2281,21 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2175,21 +2313,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2393,7 +2516,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-3.0517671257541679E-6</c:v>
+                  <c:v>-7.1208189348679038E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3084,7 +3207,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="13">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983037</v>
+        <v>-983033</v>
       </c>
       <c r="F13" s="10"/>
     </row>
@@ -3461,12 +3584,12 @@
       <c r="K34" s="26"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="47" t="s">
+      <c r="B37" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="49"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="53"/>
     </row>
     <row r="38" spans="2:11" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B38" s="27" t="s">
@@ -3474,14 +3597,14 @@
       </c>
       <c r="C38" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D38" s="27" t="s">
         <v>39</v>
       </c>
       <c r="E38" s="29">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-3.0517671257541679E-6</v>
+        <v>-7.1208189348679038E-6</v>
       </c>
     </row>
     <row r="39" spans="2:11" ht="15.9" x14ac:dyDescent="0.4">
@@ -3542,12 +3665,12 @@
       <c r="B43" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="50">
+      <c r="C43" s="54">
         <f>E13</f>
-        <v>-983037</v>
+        <v>-983033</v>
       </c>
-      <c r="D43" s="51"/>
-      <c r="E43" s="52"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3762,21 +3885,21 @@
       <c r="B2" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="47" t="s">
         <v>76</v>
       </c>
       <c r="E2" s="39"/>
       <c r="F2" s="39"/>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="47" t="s">
         <v>77</v>
       </c>
       <c r="H2" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="48" t="s">
         <v>78</v>
       </c>
       <c r="J2" s="39" t="s">
@@ -3800,21 +3923,21 @@
       <c r="B3" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="47" t="s">
         <v>76</v>
       </c>
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="47" t="s">
         <v>77</v>
       </c>
       <c r="H3" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="49" t="s">
         <v>91</v>
       </c>
       <c r="J3" s="39" t="s">
@@ -3838,24 +3961,24 @@
       <c r="B4" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="50" t="s">
         <v>89</v>
       </c>
       <c r="E4" s="39"/>
       <c r="F4" s="39"/>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="47" t="s">
         <v>77</v>
       </c>
       <c r="H4" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="55" t="s">
+      <c r="I4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="47" t="s">
         <v>93</v>
       </c>
       <c r="K4" s="39" t="s">
@@ -3869,67 +3992,147 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
+    <row r="5" spans="1:140" ht="57.9" x14ac:dyDescent="0.4">
+      <c r="A5" s="39">
+        <v>4</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>96</v>
+      </c>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
+      <c r="G5" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="J5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="39" t="s">
+        <v>79</v>
+      </c>
       <c r="M5" s="39"/>
       <c r="N5" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
+    <row r="6" spans="1:140" ht="57.9" x14ac:dyDescent="0.4">
+      <c r="A6" s="39">
+        <v>5</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>101</v>
+      </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
+      <c r="G6" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="J6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="39" t="s">
+        <v>79</v>
+      </c>
       <c r="M6" s="39"/>
     </row>
-    <row r="7" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
+    <row r="7" spans="1:140" ht="57.9" x14ac:dyDescent="0.4">
+      <c r="A7" s="39">
+        <v>6</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>101</v>
+      </c>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
+      <c r="G7" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="J7" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="39" t="s">
+        <v>79</v>
+      </c>
       <c r="M7" s="39"/>
     </row>
-    <row r="8" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A8" s="39"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
+    <row r="8" spans="1:140" ht="57.45" x14ac:dyDescent="0.4">
+      <c r="A8" s="39">
+        <v>7</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>101</v>
+      </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
+      <c r="G8" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="39" t="s">
+        <v>79</v>
+      </c>
       <c r="M8" s="39"/>
     </row>
     <row r="9" spans="1:140" x14ac:dyDescent="0.4">

--- a/测试用例清单.xlsx
+++ b/测试用例清单.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sml\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26807FE-7211-42BE-A1EE-5D0A28A6E904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4198D4-88D5-4DE9-90FE-DA8D86FB0361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="Result">'Test Cases测试用例'!$N$2:$N$5</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,39 +36,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="140">
   <si>
-    <t>在此处概述本测试用例</t>
-  </si>
-  <si>
-    <t>……</t>
-  </si>
-  <si>
-    <t>Copy No.</t>
-  </si>
-  <si>
-    <t>&lt;Project Manager&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Team members&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Customer Representative&gt;</t>
-  </si>
-  <si>
-    <t>&lt;Others&gt;</t>
-  </si>
-  <si>
-    <t>xxx</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>测试结果分析</t>
-  </si>
-  <si>
-    <t>用例总个数</t>
+    <r>
+      <t xml:space="preserve">Test  Case Form </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+      </rPr>
+      <t>测试用例表单</t>
+    </r>
   </si>
   <si>
     <r>
@@ -79,7 +60,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>基本信息</t>
     </r>
@@ -93,11 +73,12 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>产品版本</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <r>
@@ -108,7 +89,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>密级</t>
     </r>
@@ -122,11 +102,9 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>项目名称</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -137,7 +115,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>项目</t>
     </r>
@@ -159,7 +136,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>拟制</t>
     </r>
@@ -173,7 +149,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>日期</t>
     </r>
@@ -187,7 +162,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>评审人</t>
     </r>
@@ -201,7 +175,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>批准</t>
     </r>
@@ -215,7 +188,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例数</t>
     </r>
@@ -229,10 +201,12 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>概述</t>
     </r>
+  </si>
+  <si>
+    <t>在此处概述本测试用例</t>
   </si>
   <si>
     <r>
@@ -243,7 +217,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>修订记录</t>
     </r>
@@ -257,7 +230,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>日期</t>
     </r>
@@ -279,7 +251,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>修订</t>
     </r>
@@ -296,7 +267,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>版本</t>
     </r>
@@ -310,9 +280,21 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Change Description </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+      </rPr>
+      <t>修改描述</t>
     </r>
   </si>
   <si>
@@ -324,18 +306,18 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>作者</t>
     </r>
   </si>
   <si>
+    <t>yyyy.mm.dd</t>
+  </si>
+  <si>
     <t>1.00</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>xxx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -346,7 +328,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>初稿完成</t>
     </r>
@@ -360,14 +341,9 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>作者名</t>
     </r>
-  </si>
-  <si>
-    <t>yyyy.mm.dd</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -378,7 +354,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>修改</t>
     </r>
@@ -393,7 +368,6 @@
   </si>
   <si>
     <t>……</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -404,10 +378,12 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>分发记录</t>
     </r>
+  </si>
+  <si>
+    <t>Copy No.</t>
   </si>
   <si>
     <r>
@@ -418,7 +394,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>持有者和角色</t>
     </r>
@@ -432,14 +407,27 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>分发日期</t>
     </r>
   </si>
   <si>
     <t>&lt;T.M.B&amp;C.P.M&gt;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;Project Manager&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Team members&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Customer Representative&gt;</t>
+  </si>
+  <si>
+    <t>&lt;Others&gt;</t>
+  </si>
+  <si>
+    <t>测试结果分析</t>
   </si>
   <si>
     <r>
@@ -450,7 +438,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>项</t>
     </r>
@@ -464,7 +451,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>率</t>
     </r>
@@ -478,7 +464,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>项</t>
     </r>
@@ -492,7 +477,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>率</t>
     </r>
@@ -506,7 +490,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>项</t>
     </r>
@@ -520,7 +503,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>率</t>
     </r>
@@ -534,7 +516,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>项</t>
     </r>
@@ -548,26 +529,12 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>率</t>
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Test  Case Form </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测试用例表单</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>用例总个数</t>
   </si>
   <si>
     <r>
@@ -579,9 +546,22 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Test Item </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+      </rPr>
+      <t>测试项（即功能模块或函数）</t>
     </r>
   </si>
   <si>
@@ -594,7 +574,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例标题</t>
     </r>
@@ -609,10 +588,15 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>重要级别</t>
     </r>
+  </si>
+  <si>
+    <t>是否自动用例</t>
+  </si>
+  <si>
+    <t>是否新增修改用例</t>
   </si>
   <si>
     <r>
@@ -624,11 +608,9 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>预置条件</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -640,11 +622,9 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>输入</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -656,7 +636,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>操作步骤</t>
     </r>
@@ -671,11 +650,9 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>预期结果</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -688,23 +665,386 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>实际结果</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Status
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+      </rPr>
+      <t>是否通过</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Remark </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+      </rPr>
+      <t>备注</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color indexed="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+      </rPr>
+      <t>（在此描述使用的测试方法）</t>
+    </r>
+  </si>
+  <si>
+    <t>compute_score_summary</t>
+  </si>
+  <si>
+    <t>计分函数测试：全对情况</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <r>
+      <t>"q1", True, 3000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"q2", True, 4000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>将输入数据按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AnswerRecord</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>类构造传入功能函数，查看得到的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>result</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>correct=2,wrong=0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>accuracy=100%</t>
+    </r>
+  </si>
+  <si>
+    <t>test_all_correct {'total': 2, 'correct': 2, 'wrong': 0, 'accuracy': 100, 'avg_duration_ms': 3500}</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>积分函数测试：部分对情况</t>
+  </si>
+  <si>
+    <r>
+      <t>"q1", True, 3000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"q2", False, 5000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"q3", False, 4000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"q4", True, 2000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>"q5", False, 6000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>将输入数据按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>AnswerRecord</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+      </rPr>
+      <t>类构造传入功能函数，查看得到的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>result</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>correct=2,wrong=3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>accuracy=40%</t>
+    </r>
+  </si>
+  <si>
+    <t>{'total': 5, 'correct': 2, 'wrong': 3, 'accuracy': 40, 'avg_duration_ms': 4000}</t>
   </si>
   <si>
     <t>POK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>积分函数测试：空记录</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>不报错，正常返回类数据</t>
+  </si>
+  <si>
+    <t>{'total': 0, 'correct': 0, 'wrong': 0, 'accuracy': 0, 'avg_duration_ms': 0}</t>
   </si>
   <si>
     <t>NG</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>check_content</t>
+  </si>
+  <si>
+    <t>输入内容测试：正常输入</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>我想学习</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Python </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>基础语法</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>将输入测试文本传入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>check_content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>函数，判断返回值与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>expected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+      </rPr>
+      <t>是否一致</t>
+    </r>
   </si>
   <si>
     <t>NT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>输入内容测试：包含敏感词</t>
+  </si>
+  <si>
+    <t>请帮我出一套关于赌博危害的题目</t>
+  </si>
+  <si>
+    <t>输入内容测试：空字符串</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>输入测试内容：近似敏感词</t>
+  </si>
+  <si>
+    <t>这段代码性能爆破式提升，效率翻倍</t>
+  </si>
+  <si>
+    <t>将输入测试文本传入check_content函数，判断返回值与expected是否一致</t>
   </si>
   <si>
     <r>
@@ -716,7 +1056,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>使用说明</t>
     </r>
@@ -730,7 +1069,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例表包含两个表单：</t>
     </r>
@@ -747,7 +1085,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>基本信息</t>
     </r>
@@ -764,7 +1101,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>表单和</t>
     </r>
@@ -781,7 +1117,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例</t>
     </r>
@@ -798,7 +1133,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>表单。</t>
     </r>
@@ -812,7 +1146,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>本测试用例模板支持分层。</t>
     </r>
@@ -826,7 +1159,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>项目组如果需要多级分层，可在</t>
     </r>
@@ -843,7 +1175,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>页面中的</t>
     </r>
@@ -860,7 +1191,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试项</t>
     </r>
@@ -877,7 +1207,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>和</t>
     </r>
@@ -894,7 +1223,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例</t>
     </r>
@@ -911,7 +1239,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>之间增加列。例如增加</t>
     </r>
@@ -928,7 +1255,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试子项</t>
     </r>
@@ -945,7 +1271,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>。</t>
     </r>
@@ -959,7 +1284,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例的统计使用小测试用例统计，自动统计。</t>
     </r>
@@ -973,7 +1297,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>本测试用例表单不能作为测试记录使用。</t>
     </r>
@@ -987,7 +1310,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例的编号应符合测试策略中对编号规则的要求。例如，</t>
     </r>
@@ -1004,7 +1326,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>项目编码</t>
     </r>
@@ -1021,7 +1342,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>（或</t>
     </r>
@@ -1038,7 +1358,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>，</t>
     </r>
@@ -1055,7 +1374,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>）</t>
     </r>
@@ -1072,7 +1390,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>。</t>
     </r>
@@ -1086,7 +1403,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>重要级别定义为：</t>
     </r>
@@ -1103,7 +1419,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>描述测试用例的重要级别：高</t>
     </r>
@@ -1120,7 +1435,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>中</t>
     </r>
@@ -1137,7 +1451,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>低</t>
     </r>
@@ -1149,7 +1462,6 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1160,7 +1472,6 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>预期输出：</t>
     </r>
@@ -1177,11 +1488,9 @@
         <sz val="11"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>提供测试执行的预期结果</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1200,7 +1509,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>实际输出</t>
     </r>
@@ -1217,7 +1525,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">提供测试结果
 </t>
@@ -1235,7 +1542,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">测试通过
 </t>
@@ -1253,7 +1559,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">部分通过
 </t>
@@ -1271,7 +1576,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">不能通过
 </t>
@@ -1289,7 +1593,6 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试用例错误</t>
     </r>
@@ -1306,333 +1609,104 @@
         <sz val="12"/>
         <rFont val="宋体"/>
         <family val="3"/>
-        <charset val="134"/>
       </rPr>
       <t>测试无法执行</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Change Description </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>修改描述</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>knowledge_repository</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Status
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>是否通过</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>知识库仓储测试：新增文档</t>
   </si>
   <si>
-    <t>是否自动用例</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>mock aiomysql连接池</t>
   </si>
   <si>
-    <t>是否新增修改用例</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>doc_id="doc_1", user_id=1, file_name="a.pdf", file_type="pdf", file_size=1024</t>
   </si>
   <si>
-    <t>OK</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>调用create_document函数，检查cursor.execute执行的SQL与参数</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Remark </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>备注</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color indexed="10"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（在此描述使用的测试方法）</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>知识库仓储测试：更新文档状态（就绪）</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Test Item </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测试项（即功能模块或函数）</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>doc_id="doc_1", status="ready", chunk_count=5</t>
   </si>
   <si>
-    <t>compute_score_summary</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>调用update_document_status函数，检查cursor.execute执行的SQL与参数</t>
   </si>
   <si>
-    <t>中</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>知识库仓储测试：更新文档状态（失败）</t>
   </si>
   <si>
-    <t>无</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>doc_id="doc_1", status="failed", error_message="文档解析失败"</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>将输入数据按</t>
-    </r>
+    <t>知识库仓储测试：查询文档存在</t>
+  </si>
+  <si>
+    <t>doc_id="doc_1", user_id=1，fetchone返回文档行</t>
+  </si>
+  <si>
+    <t>调用get_document函数，检查SQL过滤条件、参数及返回字典</t>
+  </si>
+  <si>
+    <t>知识库仓储测试：查询文档不存在</t>
+  </si>
+  <si>
+    <t>doc_id="doc_missing", user_id=1，fetchone返回None</t>
+  </si>
+  <si>
+    <t>调用get_document函数，查看返回值</t>
+  </si>
+  <si>
+    <t>知识库仓储测试：文档列表</t>
+  </si>
+  <si>
+    <t>user_id=1，fetchall返回两行（doc_1 ready / doc_2 processing）</t>
+  </si>
+  <si>
+    <t>调用list_documents函数，检查返回列表及字段映射</t>
+  </si>
+  <si>
+    <t>返回2个字典，doc_id与status各自正确</t>
+  </si>
+  <si>
+    <t>知识库仓储测试：文档列表为空</t>
+  </si>
+  <si>
+    <t>user_id=1，fetchall返回[]</t>
+  </si>
+  <si>
+    <t>调用list_documents函数，查看返回值</t>
+  </si>
+  <si>
+    <t>知识库仓储测试：删除文档</t>
+  </si>
+  <si>
+    <t>doc_id="doc_1", user_id=1</t>
+  </si>
+  <si>
+    <t>调用delete_document函数，检查cursor.execute执行的SQL与参数</t>
+  </si>
+  <si>
+    <t>("doc_1", 1, "a.pdf", "pdf", 1024)</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>("ready", 5, None, "doc_1")</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>AnswerRecord</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>类构造传入功能函数，查看得到的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>result</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>test_all_correct {'total': 2, 'correct': 2, 'wrong': 0, 'accuracy': 100, 'avg_duration_ms': 3500}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>"q1", True, 3000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>"q2", True, 4000</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>correct=2,wrong=0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>accuracy=100%</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>计分函数测试：全对情况</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>积分函数测试：部分对情况</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>"q1", True, 3000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>"q2", False, 5000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>"q3", False, 4000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>"q4", True, 2000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>"q5", False, 6000</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{'total': 5, 'correct': 2, 'wrong': 3, 'accuracy': 40, 'avg_duration_ms': 4000}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>correct=2,wrong=3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>accuracy=40%</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>积分函数测试：空记录</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>[]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>将输入数据按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AnswerRecord</t>
+      <t>("failed", 0, "</t>
     </r>
     <r>
       <rPr>
@@ -1641,7 +1715,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>类构造传入功能函数，查看得到的</t>
+      <t>文档解析失败</t>
     </r>
     <r>
       <rPr>
@@ -1649,43 +1723,19 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>result</t>
+      <t>", "doc_1")</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{'total': 0, 'correct': 0, 'wrong': 0, 'accuracy': 0, 'avg_duration_ms': 0}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>不报错，正常返回类数据</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>check_content</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>输入内容测试：正常输入</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>中</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="1"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>我想学习</t>
+      <t>返回</t>
     </r>
     <r>
       <rPr>
@@ -1693,28 +1743,16 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> Python </t>
+      <t>doc_id="doc_1"</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="1"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>基础语法</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>将输入测试文本传入</t>
+      <t>、</t>
     </r>
     <r>
       <rPr>
@@ -1722,16 +1760,16 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>check_content</t>
+      <t>status="ready"</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="1"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>函数，判断返回值与</t>
+      <t>、</t>
     </r>
     <r>
       <rPr>
@@ -1739,50 +1777,142 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>expected</t>
+      <t>chunk_count=5</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>返回空列表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[]</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
-        <family val="1"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>是否一致</t>
+      <t>，不返回</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>None</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>输入内容测试：包含敏感词</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>("doc_1", 1)</t>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>高</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>参数一致</t>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>请帮我出一套关于赌博危害的题目</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <r>
+      <t>SQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>与参数一致</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>输入内容测试：空字符串</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>返回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>None</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>""</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>长度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，字段正确</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>输入测试内容：近似敏感词</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>这段代码性能爆破式提升，效率翻倍</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>将输入测试文本传入check_content函数，判断返回值与expected是否一致</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>返回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>[]</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1793,14 +1923,123 @@
     <numFmt numFmtId="176" formatCode="yy\.mm\.dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\.mm\.dd"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="9"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="宋体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1812,99 +2051,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="9"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="宋体"/>
       <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="1"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <family val="1"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1918,31 +2067,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="41"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="26"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="27"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="47"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2152,167 +2296,156 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2346,6 +2479,25 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr sz="1050" b="0" i="0" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>测试结果</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
@@ -2355,34 +2507,10 @@
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="25400">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:view3D>
       <c:rotX val="25"/>
-      <c:hPercent val="50"/>
       <c:rotY val="0"/>
       <c:rAngAx val="0"/>
       <c:perspective val="0"/>
@@ -2434,7 +2562,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-2581-4FE8-9D21-ACD61F56A3DC}"/>
+                <c16:uniqueId val="{00000001-F159-40B8-9B5D-5B28934054AE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2451,7 +2579,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-2581-4FE8-9D21-ACD61F56A3DC}"/>
+                <c16:uniqueId val="{00000003-F159-40B8-9B5D-5B28934054AE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2468,7 +2596,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-2581-4FE8-9D21-ACD61F56A3DC}"/>
+                <c16:uniqueId val="{00000005-F159-40B8-9B5D-5B28934054AE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2485,7 +2613,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-2581-4FE8-9D21-ACD61F56A3DC}"/>
+                <c16:uniqueId val="{00000007-F159-40B8-9B5D-5B28934054AE}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2516,7 +2644,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-7.1208189348679038E-6</c:v>
+                  <c:v>-1.5259021896696422E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2532,7 +2660,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-2581-4FE8-9D21-ACD61F56A3DC}"/>
+              <c16:uniqueId val="{00000008-F159-40B8-9B5D-5B28934054AE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2572,19 +2700,13 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="3175">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr/>
+        <a:bodyPr anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="965" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:defRPr sz="965" b="0" i="0" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -2599,7 +2721,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="0"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2612,27 +2734,10 @@
       <a:prstDash val="solid"/>
     </a:ln>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" baseline="0">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:latin typeface="Arial"/>
-          <a:ea typeface="Arial"/>
-          <a:cs typeface="Arial"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
   <c:printSettings>
-    <c:headerFooter alignWithMargins="0"/>
-    <c:pageMargins b="1" l="0.75" r="0.75" t="1" header="0.5" footer="0.5"/>
-    <c:pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -2654,16 +2759,14 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2055" name="图表 1" hidden="1">
+        <xdr:cNvPr id="2" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007080000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2677,7 +2780,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
@@ -2692,61 +2795,27 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2056" name="Picture 4">
+        <xdr:cNvPr id="3" name="/xl/media/image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008080000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="152400" y="104775"/>
-          <a:ext cx="2828925" cy="371475"/>
-        </a:xfrm>
+      <xdr:spPr>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2797,74 +2866,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2876,23 +2885,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2902,23 +2911,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2926,26 +2935,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -2980,17 +2986,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -3007,17 +3013,11 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:L43"/>
   <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3030,7 +3030,7 @@
     <row r="1" spans="2:12" ht="9.9" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:12" ht="23.15" x14ac:dyDescent="0.5">
       <c r="B2" s="6" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
@@ -3069,7 +3069,7 @@
     <row r="5" spans="2:12" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B6" s="9" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -3084,105 +3084,105 @@
     </row>
     <row r="7" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B7" s="9" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="9" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="10"/>
     </row>
     <row r="8" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B8" s="9" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="9" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
       <c r="J8" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="10"/>
     </row>
     <row r="9" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="9" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
       <c r="J9" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="10"/>
     </row>
     <row r="10" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B10" s="9" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="9" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
       <c r="J10" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B11" s="9" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="9" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="11" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="10"/>
@@ -3201,13 +3201,13 @@
     </row>
     <row r="13" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B13" s="9" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="13">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
-        <v>-983033</v>
+        <v>-983025</v>
       </c>
       <c r="F13" s="10"/>
     </row>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="15" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B15" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="16" spans="2:12" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="4" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="11"/>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="18" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B18" s="9" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -3276,16 +3276,16 @@
     </row>
     <row r="19" spans="2:12" ht="47.15" x14ac:dyDescent="0.4">
       <c r="B19" s="15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
@@ -3293,22 +3293,22 @@
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
       <c r="K19" s="15" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="L19" s="10"/>
     </row>
     <row r="20" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B20" s="17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
@@ -3316,22 +3316,22 @@
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L20" s="10"/>
     </row>
     <row r="21" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B21" s="17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C21" s="18">
         <v>1.01</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
@@ -3339,7 +3339,7 @@
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L21" s="10"/>
     </row>
@@ -3347,10 +3347,10 @@
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
       <c r="D22" s="11" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
@@ -3358,22 +3358,22 @@
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L22" s="10"/>
     </row>
     <row r="23" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B23" s="17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C23" s="18">
         <v>1.02</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
@@ -3381,22 +3381,22 @@
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L23" s="10"/>
     </row>
     <row r="24" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B24" s="17" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
@@ -3404,22 +3404,22 @@
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L24" s="10"/>
     </row>
     <row r="25" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B25" s="17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C25" s="18">
         <v>2</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
@@ -3427,7 +3427,7 @@
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L25" s="10"/>
     </row>
@@ -3445,7 +3445,7 @@
     </row>
     <row r="27" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B27" s="9" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="28" spans="2:12" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B28" s="20" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
@@ -3472,7 +3472,7 @@
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="10"/>
@@ -3482,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
@@ -3491,7 +3491,7 @@
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
       <c r="J29" s="17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="10"/>
@@ -3501,7 +3501,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
@@ -3510,7 +3510,7 @@
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="10"/>
@@ -3520,7 +3520,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
@@ -3529,7 +3529,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
       <c r="J31" s="17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K31" s="17"/>
       <c r="L31" s="10"/>
@@ -3539,7 +3539,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
@@ -3548,7 +3548,7 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K32" s="17"/>
       <c r="L32" s="10"/>
@@ -3558,7 +3558,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -3567,7 +3567,7 @@
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
       <c r="J33" s="23" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K33" s="24"/>
     </row>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="51" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C37" s="52"/>
       <c r="D37" s="52"/>
@@ -3593,30 +3593,30 @@
     </row>
     <row r="38" spans="2:11" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B38" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E38" s="29">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-7.1208189348679038E-6</v>
+        <v>-1.5259021896696422E-5</v>
       </c>
     </row>
     <row r="39" spans="2:11" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B39" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=POK"))</f>
         <v>0</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E39" s="29">
         <f>IF(E13=0,0,C39/E13)</f>
@@ -3625,14 +3625,14 @@
     </row>
     <row r="40" spans="2:11" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B40" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NG"))</f>
         <v>0</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E40" s="29">
         <f>IF(E13=0,0,C40/E13)</f>
@@ -3641,14 +3641,14 @@
     </row>
     <row r="41" spans="2:11" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B41" s="30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41" s="31">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NT"))</f>
         <v>0</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E41" s="32">
         <f>IF(E13=0,0,C41/E13)</f>
@@ -3663,11 +3663,11 @@
     </row>
     <row r="43" spans="2:11" ht="15.9" x14ac:dyDescent="0.4">
       <c r="B43" s="3" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C43" s="54">
         <f>E13</f>
-        <v>-983033</v>
+        <v>-983025</v>
       </c>
       <c r="D43" s="55"/>
       <c r="E43" s="56"/>
@@ -3677,19 +3677,14 @@
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="C43:E43"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
+  <phoneticPr fontId="22" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="Sheet2">
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:EJ12389"/>
   <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3712,10 +3707,10 @@
   <sheetData>
     <row r="1" spans="1:140" ht="46.3" x14ac:dyDescent="0.4">
       <c r="A1" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="C1" s="37" t="s">
         <v>48</v>
@@ -3724,31 +3719,31 @@
         <v>49</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F1" s="46" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J1" s="37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M1" s="37" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="N1" s="38"/>
       <c r="O1" s="38"/>
@@ -3883,37 +3878,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="D2" s="47" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E2" s="39"/>
       <c r="F2" s="39"/>
       <c r="G2" s="47" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="I2" s="48" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="J2" s="39" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M2" s="39"/>
       <c r="N2" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:140" ht="101.15" x14ac:dyDescent="0.4">
@@ -3921,37 +3916,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
       <c r="G3" s="47" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="H3" s="39" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I3" s="49" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="J3" s="39" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="L3" s="39" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M3" s="39"/>
       <c r="N3" s="5" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:140" ht="85.3" x14ac:dyDescent="0.4">
@@ -3959,37 +3954,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E4" s="39"/>
       <c r="F4" s="39"/>
       <c r="G4" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="J4" s="47" t="s">
-        <v>93</v>
-      </c>
       <c r="K4" s="39" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="L4" s="39" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M4" s="39"/>
       <c r="N4" s="5" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:140" ht="57.9" x14ac:dyDescent="0.4">
@@ -3997,24 +3992,24 @@
         <v>4</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
       <c r="G5" s="47" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="H5" s="48" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="J5" s="39" t="b">
         <v>1</v>
@@ -4023,11 +4018,11 @@
         <v>1</v>
       </c>
       <c r="L5" s="39" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M5" s="39"/>
       <c r="N5" s="5" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:140" ht="57.9" x14ac:dyDescent="0.4">
@@ -4035,24 +4030,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
       <c r="G6" s="47" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="H6" s="49" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="I6" s="48" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="J6" s="39" t="b">
         <v>0</v>
@@ -4061,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="39" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M6" s="39"/>
     </row>
@@ -4070,24 +4065,24 @@
         <v>6</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
       <c r="G7" s="47" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="J7" s="39" t="b">
         <v>1</v>
@@ -4096,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="39" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M7" s="39"/>
     </row>
@@ -4105,24 +4100,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D8" s="47" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
       <c r="G8" s="47" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="H8" s="49" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="I8" s="49" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="J8" s="39" t="b">
         <v>1</v>
@@ -4131,128 +4126,288 @@
         <v>1</v>
       </c>
       <c r="L8" s="39" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M8" s="39"/>
     </row>
-    <row r="9" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A9" s="39"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
+    <row r="9" spans="1:140" ht="71.150000000000006" x14ac:dyDescent="0.4">
+      <c r="A9" s="39">
+        <v>8</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>61</v>
+      </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
+      <c r="G9" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J9" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="K9" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="L9" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="M9" s="39"/>
     </row>
-    <row r="10" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A10" s="39"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
+    <row r="10" spans="1:140" ht="71.150000000000006" x14ac:dyDescent="0.4">
+      <c r="A10" s="39">
+        <v>9</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>61</v>
+      </c>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
+      <c r="G10" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="L10" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="M10" s="39"/>
     </row>
-    <row r="11" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A11" s="39"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
+    <row r="11" spans="1:140" ht="71.150000000000006" x14ac:dyDescent="0.4">
+      <c r="A11" s="39">
+        <v>10</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>75</v>
+      </c>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
+      <c r="G11" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="K11" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="M11" s="39"/>
     </row>
-    <row r="12" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A12" s="39"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
+    <row r="12" spans="1:140" ht="57" x14ac:dyDescent="0.4">
+      <c r="A12" s="39">
+        <v>11</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>75</v>
+      </c>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
+      <c r="G12" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="K12" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="L12" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="M12" s="39"/>
     </row>
-    <row r="13" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A13" s="39"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
+    <row r="13" spans="1:140" ht="57" x14ac:dyDescent="0.4">
+      <c r="A13" s="39">
+        <v>12</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>61</v>
+      </c>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
+      <c r="G13" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="J13" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="K13" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="L13" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="M13" s="39"/>
     </row>
-    <row r="14" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A14" s="39"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
+    <row r="14" spans="1:140" ht="71.150000000000006" x14ac:dyDescent="0.4">
+      <c r="A14" s="39">
+        <v>13</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>61</v>
+      </c>
       <c r="E14" s="39"/>
       <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
+      <c r="G14" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="K14" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="L14" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="M14" s="39"/>
     </row>
-    <row r="15" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
+    <row r="15" spans="1:140" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A15" s="39">
+        <v>14</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>61</v>
+      </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
+      <c r="G15" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15" s="58" t="s">
+        <v>133</v>
+      </c>
+      <c r="K15" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="L15" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="M15" s="39"/>
     </row>
-    <row r="16" spans="1:140" x14ac:dyDescent="0.4">
-      <c r="A16" s="39"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
+    <row r="16" spans="1:140" ht="71.150000000000006" x14ac:dyDescent="0.4">
+      <c r="A16" s="39">
+        <v>15</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>75</v>
+      </c>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
+      <c r="G16" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="J16" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="K16" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="39" t="s">
+        <v>67</v>
+      </c>
       <c r="M16" s="39"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -41975,8 +42130,7 @@
       <c r="L12389" s="39"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showErrorMessage="1" errorTitle="Warning" error="Invalide Data" sqref="K2" xr:uid="{00000000-0002-0000-0100-000000000000}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12390:L65536" xr:uid="{00000000-0002-0000-0100-000001000000}">
@@ -41986,15 +42140,12 @@
       <formula1>Result</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="85" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
@@ -42005,7 +42156,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.45" x14ac:dyDescent="0.35">
       <c r="A1" s="41" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="2"/>
@@ -42015,7 +42166,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -42024,7 +42175,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -42033,7 +42184,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2"/>
     </row>
@@ -42042,16 +42193,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="42">
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -42060,7 +42211,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -42069,7 +42220,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2"/>
     </row>
@@ -42078,23 +42229,20 @@
         <v>8</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" ht="73.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="44">
         <v>9</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
+  <phoneticPr fontId="22" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/测试用例清单.xlsx
+++ b/测试用例清单.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="213">
   <si>
     <r>
       <rPr>
@@ -1116,40 +1116,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>将输入数据按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>AnswerRecord</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>类构造传入功能函数，查看得到的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>result</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
@@ -1593,22 +1559,263 @@
     <t>调用delete_document函数，检查cursor.execute执行的SQL与参数</t>
   </si>
   <si>
+    <t>handle_upload</t>
+  </si>
+  <si>
     <t>知识库功能测试：上传大于10MB的文档</t>
+  </si>
+  <si>
+    <r>
+      <t>已配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> kb_max_file_size_mb=10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>filename=big.pdf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>content=10MB+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>字节</t>
+    </r>
+  </si>
+  <si>
+    <t>调用handle_upload</t>
+  </si>
+  <si>
+    <r>
+      <t>抛出异常：文件大小超过限制（最大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 10MB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>抛出异常：文件大小超过限制（最大 10MB）</t>
   </si>
   <si>
     <t>知识库功能测试：上传非PDF/txt/word/Markdown文件</t>
   </si>
   <si>
+    <t>filename=virus.exe，content=任意字节</t>
+  </si>
+  <si>
+    <r>
+      <t>抛出异常：不支持的文件格式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>exe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，仅支持</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> PDF/Word/Markdown/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文本文件</t>
+    </r>
+  </si>
+  <si>
+    <t>抛出异常：不支持的文件格式：exe，仅支持 PDF/Word/Markdown/文本文件</t>
+  </si>
+  <si>
     <t>知识库功能测试：扩展名提取</t>
   </si>
   <si>
+    <t>report.PDF / notes.txt / archive.tar.gz / no_extension</t>
+  </si>
+  <si>
+    <t>调用 _get_extension</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pdf / txt / gz / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（空字符串</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> {'report.PDF': 'pdf', 'notes.txt': 'txt', 'archive.tar.gz': 'gz', 'no_extension': ''} </t>
+  </si>
+  <si>
     <t>知识库功能测试：解析文件并生成题目</t>
+  </si>
+  <si>
+    <t>文档加载服务与向量库可用</t>
+  </si>
+  <si>
+    <r>
+      <t>doc_id=doc_test123</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>file_path=/tmp/test.pdf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">mock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>返回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> chunk</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>调用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> _process_document</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，观察状态更新</t>
+    </r>
+  </si>
+  <si>
+    <t>文档状态更新为 ready，chunk_count=3</t>
+  </si>
+  <si>
+    <t>update_document_status("doc_test123", "ready", chunk_count=3)</t>
   </si>
   <si>
     <t>create_token / decode_token</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>JWT测试：生成</t>
     </r>
     <r>
@@ -1630,6 +1837,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>已配置</t>
     </r>
     <r>
@@ -1662,6 +1874,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>调用</t>
     </r>
     <r>
@@ -1711,6 +1928,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>已配置</t>
     </r>
     <r>
@@ -1724,6 +1946,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>合法</t>
     </r>
     <r>
@@ -1752,6 +1979,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>抛出异常：过期</t>
     </r>
     <r>
@@ -1779,6 +2011,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>无</t>
     </r>
     <r>
@@ -1800,6 +2037,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>调用</t>
     </r>
     <r>
@@ -1815,19 +2057,511 @@
     <t>抛出异常：未登录或登录已过期</t>
   </si>
   <si>
-    <t>答题功能测试：答题记录生成</t>
+    <t>handle_quiz_generate</t>
   </si>
   <si>
-    <t>答题功能测试：闯关记录保存</t>
+    <t>出题测试:登录校验</t>
   </si>
   <si>
-    <t>答题功能测试：生成海报</t>
+    <t>QuizGenerateRequest(..., doc_id="doc_1"), user_id=None</t>
   </si>
   <si>
-    <t>答题功能测试：下一组题目生成</t>
+    <r>
+      <t>调用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> handle_quiz_generate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，捕获异常</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
-    <t>用户界面测试：用户头像上传</t>
+    <r>
+      <t>抛出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> KnowledgeBaseError</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，错误信息匹配</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>先登录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>出题测试：文件不属于该用户</t>
+  </si>
+  <si>
+    <t>QuizGenerateRequest(..., doc_id="doc_missing"), user_id=1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">抛出 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>KnowledgeBaseError</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，错误信息匹配"不存在"</t>
+    </r>
+  </si>
+  <si>
+    <t>出题测试：文档状态校验</t>
+  </si>
+  <si>
+    <t>上传文档之后且正在处理中</t>
+  </si>
+  <si>
+    <t>QuizGenerateRequest(..., doc_id="doc_1"), user_id=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">调用 handle_quiz_generate，捕获异常 </t>
+  </si>
+  <si>
+    <r>
+      <t>抛出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> KnowledgeBaseError</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，错误信息匹配</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尚未就绪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>create_quiz_task</t>
+  </si>
+  <si>
+    <t>出题测试：前置校验失败</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">get_document </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>返回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">task_repository.create_task </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> asyncio.create_task </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>被</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> mock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> create_quiz_task</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，捕获异常后检查任务创建与调度情况</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>抛出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> KnowledgeBaseError</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>抛出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> KnowledgeBaseError</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">task_repository.create_task </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未被调用；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">asyncio.create_task </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未被调用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>出题测试：前置校验通过</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">get_document </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>返回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> ready </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文档；任务仓库与事件循环调度均被</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> mock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>调用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> create_quiz_task</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，检查返回值与两次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> create_task </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">task_repository.create_task </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>被调用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">asyncio.create_task </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>被调用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次</t>
+    </r>
   </si>
   <si>
     <t>用户界面测试：用户昵称填写超长字符串</t>
@@ -2466,7 +3200,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\.mm\.dd"/>
     <numFmt numFmtId="177" formatCode="yy\.mm\.dd"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="34">
     <font>
       <sz val="12"/>
       <name val="Arial"/>
@@ -2502,21 +3236,6 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2698,22 +3417,12 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2721,12 +3430,6 @@
       <b/>
       <sz val="12"/>
       <color indexed="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -3258,19 +3961,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3279,131 +3994,119 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3440,16 +4143,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3469,10 +4163,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3521,14 +4215,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="10" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3800,7 +4494,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-2.03456729839981e-5</c:v>
+                  <c:v>-2.95012258267973e-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4178,648 +4872,648 @@
   <sheetData>
     <row r="1" ht="9.9" customHeight="1"/>
     <row r="2" ht="23" spans="2:11">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
     </row>
     <row r="5" ht="3.9" customHeight="1"/>
     <row r="6" spans="2:12">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="26"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="23"/>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="22" t="s">
+      <c r="F7" s="20"/>
+      <c r="G7" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="23" t="s">
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="26"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="23"/>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="22" t="s">
+      <c r="F8" s="20"/>
+      <c r="G8" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="23" t="s">
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="23"/>
-      <c r="L8" s="26"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="23"/>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="23"/>
-      <c r="G9" s="22" t="s">
+      <c r="F9" s="20"/>
+      <c r="G9" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="23" t="s">
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="26"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="23"/>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="22" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="23" t="s">
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="23"/>
-      <c r="L10" s="26"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="23"/>
     </row>
     <row r="11" spans="2:12">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="22" t="s">
+      <c r="F11" s="20"/>
+      <c r="G11" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="23" t="s">
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="K11" s="23"/>
-      <c r="L11" s="26"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="23"/>
     </row>
     <row r="12" ht="3.9" customHeight="1" spans="2:11">
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="25">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="22">
         <f>65535-COUNTBLANK('Test Cases测试用例'!A:A)</f>
         <v>-983010</v>
       </c>
-      <c r="F13" s="26"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" ht="3.9" customHeight="1" spans="2:5">
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="26"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="23"/>
     </row>
     <row r="16" ht="18.9" customHeight="1" spans="2:12">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="26"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="23"/>
     </row>
     <row r="17" ht="3.9" customHeight="1" spans="2:11">
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
     </row>
     <row r="18" spans="2:12">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="26"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="23"/>
     </row>
     <row r="19" ht="46.5" spans="2:12">
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="29" t="s">
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="L19" s="26"/>
+      <c r="L19" s="23"/>
     </row>
     <row r="20" spans="2:12">
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23" t="s">
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="26"/>
+      <c r="L20" s="23"/>
     </row>
     <row r="21" spans="2:12">
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="29">
         <v>1.01</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23" t="s">
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="26"/>
+      <c r="L21" s="23"/>
     </row>
     <row r="22" spans="2:12">
-      <c r="B22" s="31"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="23" t="s">
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23" t="s">
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L22" s="26"/>
+      <c r="L22" s="23"/>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="29">
         <v>1.02</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23" t="s">
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L23" s="26"/>
+      <c r="L23" s="23"/>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23" t="s">
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="26"/>
+      <c r="L24" s="23"/>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="29">
         <v>2</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23" t="s">
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="L25" s="26"/>
+      <c r="L25" s="23"/>
     </row>
     <row r="26" ht="3.9" customHeight="1" spans="2:11">
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="26"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="23"/>
     </row>
     <row r="28" spans="2:12">
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22" t="s">
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="26"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="2:12">
-      <c r="B29" s="23">
+      <c r="B29" s="20">
         <v>1</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="31" t="s">
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K29" s="31"/>
-      <c r="L29" s="26"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="2:12">
-      <c r="B30" s="23">
+      <c r="B30" s="20">
         <v>2</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="31" t="s">
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K30" s="31"/>
-      <c r="L30" s="26"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="23"/>
     </row>
     <row r="31" spans="2:12">
-      <c r="B31" s="23">
+      <c r="B31" s="20">
         <v>3</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="31" t="s">
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K31" s="31"/>
-      <c r="L31" s="26"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="2:12">
-      <c r="B32" s="23">
+      <c r="B32" s="20">
         <v>4</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="31" t="s">
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="31"/>
-      <c r="L32" s="26"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="23"/>
     </row>
     <row r="33" spans="2:11">
-      <c r="B33" s="35">
+      <c r="B33" s="32">
         <v>5</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="55" t="s">
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="K33" s="56"/>
+      <c r="K33" s="53"/>
     </row>
     <row r="34" spans="2:11">
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="57"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="54"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="2:5">
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="40"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="37"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="42">
+      <c r="C38" s="39">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>20</v>
+        <v>29</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="D38" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="E38" s="43">
+      <c r="E38" s="40">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>-2.03456729839981e-5</v>
+        <v>-2.95012258267973e-5</v>
       </c>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="42">
+      <c r="C39" s="39">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=POK"))</f>
         <v>0</v>
       </c>
-      <c r="D39" s="41" t="s">
+      <c r="D39" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="40">
         <f>IF(E13=0,0,C39/E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="42">
+      <c r="C40" s="39">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NG"))</f>
         <v>0</v>
       </c>
-      <c r="D40" s="41" t="s">
+      <c r="D40" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="40">
         <f>IF(E13=0,0,C40/E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="44" t="s">
+      <c r="B41" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="45">
+      <c r="C41" s="42">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NT"))</f>
         <v>0</v>
       </c>
-      <c r="D41" s="44" t="s">
+      <c r="D41" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E41" s="46">
+      <c r="E41" s="43">
         <f>IF(E13=0,0,C41/E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" ht="3" customHeight="1" spans="2:5">
-      <c r="B42" s="47"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="50"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="47"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="52">
+      <c r="C43" s="49">
         <f>E13</f>
         <v>-983010</v>
       </c>
-      <c r="D43" s="53"/>
-      <c r="E43" s="54"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5083,20 +5777,20 @@
         <v>69</v>
       </c>
       <c r="I3" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="K3" s="12" t="s">
         <v>71</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>67</v>
       </c>
       <c r="M3" s="12"/>
       <c r="N3" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" ht="84" spans="1:14">
@@ -5107,10 +5801,10 @@
         <v>59</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
@@ -5118,23 +5812,23 @@
         <v>62</v>
       </c>
       <c r="H4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="13" t="s">
+      <c r="K4" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="L4" s="12" t="s">
         <v>67</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:14">
@@ -5142,10 +5836,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>61</v>
@@ -5156,10 +5850,10 @@
         <v>62</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J5" s="12" t="b">
         <v>1</v>
@@ -5172,7 +5866,7 @@
       </c>
       <c r="M5" s="12"/>
       <c r="N5" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" ht="56" spans="1:13">
@@ -5180,13 +5874,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -5194,10 +5888,10 @@
         <v>62</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J6" s="12" t="b">
         <v>0</v>
@@ -5215,13 +5909,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -5229,10 +5923,10 @@
         <v>62</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J7" s="12" t="b">
         <v>1</v>
@@ -5250,13 +5944,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
@@ -5264,10 +5958,10 @@
         <v>62</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" s="12" t="b">
         <v>1</v>
@@ -5285,10 +5979,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>61</v>
@@ -5302,13 +5996,13 @@
         <v>62</v>
       </c>
       <c r="I9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="K9" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>96</v>
       </c>
       <c r="L9" s="12" t="s">
         <v>67</v>
@@ -5320,10 +6014,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>61</v>
@@ -5331,19 +6025,19 @@
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="I10" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="J10" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="K10" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>103</v>
       </c>
       <c r="L10" s="12" t="s">
         <v>67</v>
@@ -5355,10 +6049,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>61</v>
@@ -5366,19 +6060,19 @@
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H11" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="J11" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="K11" s="13" t="s">
         <v>107</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>108</v>
       </c>
       <c r="L11" s="12" t="s">
         <v>67</v>
@@ -5390,30 +6084,30 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H12" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>108</v>
+      <c r="K12" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="L12" s="12" t="s">
         <v>67</v>
@@ -5425,30 +6119,30 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="J13" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="K13" s="12" t="s">
         <v>115</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>116</v>
       </c>
       <c r="L13" s="12" t="s">
         <v>67</v>
@@ -5460,10 +6154,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>61</v>
@@ -5471,19 +6165,19 @@
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
       <c r="G14" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H14" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="J14" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="K14" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>121</v>
       </c>
       <c r="L14" s="12" t="s">
         <v>67</v>
@@ -5495,10 +6189,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>61</v>
@@ -5506,19 +6200,19 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
       <c r="G15" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H15" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="J15" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="K15" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>126</v>
       </c>
       <c r="L15" s="12" t="s">
         <v>67</v>
@@ -5530,10 +6224,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>61</v>
@@ -5541,19 +6235,19 @@
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
       <c r="G16" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="J16" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="K16" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>131</v>
       </c>
       <c r="L16" s="12" t="s">
         <v>67</v>
@@ -5565,110 +6259,174 @@
         <v>16</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H17" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I17" s="12" t="s">
-        <v>134</v>
+      <c r="J17" s="12" t="s">
+        <v>115</v>
       </c>
-      <c r="J17" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>108</v>
+      <c r="K17" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="L17" s="12" t="s">
         <v>67</v>
       </c>
       <c r="M17" s="12"/>
     </row>
-    <row r="18" ht="28" spans="1:13">
+    <row r="18" ht="56" spans="1:13">
       <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="12"/>
+      <c r="B18" s="12" t="s">
+        <v>134</v>
+      </c>
       <c r="C18" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="12"/>
+      <c r="D18" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="12"/>
+      <c r="G18" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M18" s="12"/>
     </row>
-    <row r="19" ht="28" spans="1:13">
+    <row r="19" ht="84" spans="1:13">
       <c r="A19" s="12">
         <v>18</v>
       </c>
-      <c r="B19" s="12"/>
+      <c r="B19" s="12" t="s">
+        <v>134</v>
+      </c>
       <c r="C19" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="12"/>
+      <c r="H19" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M19" s="12"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" ht="98" spans="1:13">
       <c r="A20" s="12">
         <v>19</v>
       </c>
-      <c r="B20" s="12"/>
+      <c r="B20" s="12" t="s">
+        <v>134</v>
+      </c>
       <c r="C20" s="13" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
-      <c r="D20" s="13"/>
+      <c r="D20" s="13" t="s">
+        <v>61</v>
+      </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
+      <c r="G20" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M20" s="12"/>
     </row>
-    <row r="21" ht="28" spans="1:13">
+    <row r="21" ht="70" spans="1:13">
       <c r="A21" s="12">
         <v>20</v>
       </c>
-      <c r="B21" s="12"/>
+      <c r="B21" s="12" t="s">
+        <v>134</v>
+      </c>
       <c r="C21" s="13" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
-      <c r="D21" s="13"/>
+      <c r="D21" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
+      <c r="G21" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M21" s="12"/>
     </row>
     <row r="22" ht="56" spans="1:13">
@@ -5676,30 +6434,30 @@
         <v>21</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="13" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="L22" s="12" t="s">
         <v>67</v>
@@ -5711,30 +6469,30 @@
         <v>22</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="13" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="L23" s="12" t="s">
         <v>67</v>
@@ -5746,10 +6504,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>61</v>
@@ -5757,19 +6515,19 @@
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="G24" s="13" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="L24" s="12" t="s">
         <v>67</v>
@@ -5781,13 +6539,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -5795,127 +6553,209 @@
         <v>62</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="L25" s="12" t="s">
         <v>67</v>
       </c>
       <c r="M25" s="12"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" ht="70" spans="1:13">
       <c r="A26" s="12">
         <v>25</v>
       </c>
-      <c r="B26" s="12"/>
+      <c r="B26" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="C26" s="13" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
-      <c r="D26" s="12"/>
+      <c r="D26" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
+      <c r="G26" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M26" s="12"/>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" ht="80" spans="1:13">
       <c r="A27" s="12">
         <v>26</v>
       </c>
-      <c r="B27" s="12"/>
+      <c r="B27" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="C27" s="13" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
-      <c r="D27" s="12"/>
+      <c r="D27" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="E27" s="12"/>
       <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
+      <c r="G27" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M27" s="12"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" ht="70" spans="1:13">
       <c r="A28" s="12">
         <v>27</v>
       </c>
-      <c r="B28" s="12"/>
+      <c r="B28" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="C28" s="13" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
-      <c r="D28" s="12"/>
+      <c r="D28" s="13" t="s">
+        <v>61</v>
+      </c>
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
+      <c r="G28" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M28" s="12"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" ht="112" spans="1:13">
       <c r="A29" s="12">
         <v>28</v>
       </c>
-      <c r="B29" s="12"/>
+      <c r="B29" s="12" t="s">
+        <v>191</v>
+      </c>
       <c r="C29" s="13" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
-      <c r="D29" s="12"/>
+      <c r="D29" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="G29" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M29" s="12"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" ht="84" spans="1:13">
       <c r="A30" s="12">
         <v>29</v>
       </c>
-      <c r="B30" s="12"/>
+      <c r="B30" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="C30" s="13" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
-      <c r="D30" s="12"/>
+      <c r="D30" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="G30" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="M30" s="12"/>
     </row>
     <row r="31" ht="28" spans="1:13">
       <c r="A31" s="12">
         <v>30</v>
       </c>
-      <c r="B31" s="12"/>
+      <c r="B31" s="12" t="s">
+        <v>178</v>
+      </c>
       <c r="C31" s="13" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
@@ -43514,7 +44354,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showErrorMessage="1" errorTitle="Warning" error="Invalide Data" sqref="K2"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L8 L9 L18 L19 L20 L21 L25 L2:L7 L10:L17 L22:L24 L26:L12395">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L12395">
       <formula1>Result</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L12396:L65542">
@@ -43539,7 +44379,7 @@
   <sheetData>
     <row r="1" ht="15.5" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -43549,7 +44389,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -43558,7 +44398,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -43567,7 +44407,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -43576,7 +44416,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -43585,7 +44425,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -43594,7 +44434,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -43603,7 +44443,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -43612,7 +44452,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -43621,7 +44461,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
